--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{434BBAC9-6DD3-48D3-B132-FF3E494C3F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5EBD1D1-AE42-4893-9724-9B95F4055DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1004,165 +1004,237 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_won-CHE_0003</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_3</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0011</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_11</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0015</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_15</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0025</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_25</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0013</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_13</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0010</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_10</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0022</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_22</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0024</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_24</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0008</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_8</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0005</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_5</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0000</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_0</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0012</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_12</t>
+  </si>
+  <si>
     <t>distr_solelc_won-CHE_0014</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell CHE_14</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_won-CHE_0018</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell CHE_18</t>
   </si>
   <si>
+    <t>distr_solelc_won-CHE_0020</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_20</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0001</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_1</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0006</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_6</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0009</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_9</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0021</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_21</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0004</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_4</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0017</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_17</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0019</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_19</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0023</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_23</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0002</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_2</t>
+  </si>
+  <si>
     <t>distr_solelc_won-CHE_0007</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell CHE_7</t>
   </si>
   <si>
-    <t>distr_solelc_won-CHE_0000</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_0</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0012</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_12</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0003</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_3</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0017</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_17</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0019</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_19</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0023</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_23</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0024</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_24</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0008</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_8</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0005</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_5</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0020</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_20</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0001</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_1</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0006</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_6</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0011</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_11</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0015</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_15</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0025</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_25</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0010</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_10</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0022</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_22</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0013</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_13</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0009</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_9</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0021</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_21</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0004</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_4</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0002</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_2</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
+    <t>elc_won-CHE_0003,elc_spv-CHE_0003</t>
+  </si>
+  <si>
+    <t>e_CH48-225,e_CH49-225,e_CH53-225,e_CH60-225,e_w234983117-220,e_w234983117-380,e_w238138373-380,e_w260211728-225,e_w260211728-380,e_w55698557-220,e_w55698557-225,e_w802058337-220,e_w802058337-225,e_w936521586-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0011,elc_spv-CHE_0011</t>
+  </si>
+  <si>
+    <t>e_CH46-220,e_CH47-220,e_w228003081-220,e_w391576135-220,e_w391577741-220,e_w969819301-220,e_w969819301-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0015,elc_spv-CHE_0015</t>
+  </si>
+  <si>
+    <t>e_CH50-220,e_CH56-220,e_CH58-220,e_CH59-220,e_w1327084723-220,e_w281800404-220,e_w281803398-220,e_w281815404-220,e_w35487135-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0025,elc_spv-CHE_0025</t>
+  </si>
+  <si>
+    <t>e_r7933294-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0013,elc_spv-CHE_0013</t>
+  </si>
+  <si>
+    <t>e_CH15-220,e_w146225999-220,e_w159527493-220,e_w242269161-220,e_w281799252-220,e_w35002638-220,e_w35002638-380,e_w97941869-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0010,elc_spv-CHE_0010</t>
+  </si>
+  <si>
+    <t>e_CH11-220,e_w109037817-220,e_w109037817-380,e_w127004407-380,e_w127004407-400,e_w27435934-220,e_w30350721-220,e_w397960460-380,e_w397960460-400,e_w88901626-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0022,elc_spv-CHE_0022</t>
+  </si>
+  <si>
+    <t>e_CH4-220,e_CH9-220,e_w455120191-220,e_w83861269-220,e_w92798668-220,e_w92873516-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
+  </si>
+  <si>
+    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
+  </si>
+  <si>
+    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
+  </si>
+  <si>
+    <t>e_r5378910-220,e_w161853746-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0000,elc_spv-CHE_0000</t>
+  </si>
+  <si>
+    <t>e_CH51-220,e_CH51-225,e_CH51-400,e_CH52-220,e_CH57-220,e_CH57-225,e_w177392130-220,e_w177392130-400,e_w239937062-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0012,elc_spv-CHE_0012</t>
+  </si>
+  <si>
+    <t>e_CH19-220,e_CH20-220,e_CH25-220,e_CH27-220,e_CH34-220,e_CH34-380,e_CH35-220,e_CH36-220,e_CH38-220,e_CH39-220,e_CH40-220,e_w1086214433-220,e_w1092884227-220,e_w240959264-220,e_w364949845-220,e_w364949845-380</t>
+  </si>
+  <si>
     <t>elc_won-CHE_0014,elc_spv-CHE_0014</t>
   </si>
   <si>
@@ -1175,142 +1247,70 @@
     <t>e_CH3-220,e_CH6-220,e_r9310861-220,e_w11282314-220,e_w147714395-220,e_w147714395-380,e_w148015471-220,e_w22899676-220,e_w240575085-220,e_w26843160-220,e_w281809991-220,e_w50561341-220,e_w87281514-220</t>
   </si>
   <si>
+    <t>elc_won-CHE_0020,elc_spv-CHE_0020</t>
+  </si>
+  <si>
+    <t>e_CH21-220,e_CH22-220,e_CH22-380,e_CH29-220,e_CH29-380,e_CH41-380,e_w1208713169-220,e_w207993342-220,e_w207993342-380,e_w208780268-380,e_w212498548-220,e_w36348118-220,e_w365556107-220,e_w71500123-220,e_w71500123-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0001,elc_spv-CHE_0001</t>
+  </si>
+  <si>
+    <t>e_CH31-220,e_w132373704-220,e_w232662311-220,e_w44496892-220,e_w55695765-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0006,elc_spv-CHE_0006</t>
+  </si>
+  <si>
+    <t>e_w127004407-400</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
+  </si>
+  <si>
+    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
+  </si>
+  <si>
+    <t>e_CH17-380,e_w211907009-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
+  </si>
+  <si>
+    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0017,elc_spv-CHE_0017</t>
+  </si>
+  <si>
+    <t>e_CH12-220,e_CH12-380,e_CH13-220,e_CH16-380,e_CH18-220,e_CH18-380,e_w192677427-220,e_w192677427-380,e_w52738225-220,e_w52738225-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0019,elc_spv-CHE_0019</t>
+  </si>
+  <si>
+    <t>e_CH45-220,e_w281804158-220,e_w281804158-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0023,elc_spv-CHE_0023</t>
+  </si>
+  <si>
+    <t>e_w207991759-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
+  </si>
+  <si>
+    <t>e_w232662311-220</t>
+  </si>
+  <si>
     <t>elc_won-CHE_0007,elc_spv-CHE_0007</t>
   </si>
   <si>
     <t>e_CH44-220,e_w212722603-220,e_w212722603-380,e_w236819191-220,e_w758943072-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0000,elc_spv-CHE_0000</t>
-  </si>
-  <si>
-    <t>e_CH51-220,e_CH51-225,e_CH51-400,e_CH52-220,e_CH57-220,e_CH57-225,e_w177392130-220,e_w177392130-400,e_w239937062-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0012,elc_spv-CHE_0012</t>
-  </si>
-  <si>
-    <t>e_CH19-220,e_CH20-220,e_CH25-220,e_CH27-220,e_CH34-220,e_CH34-380,e_CH35-220,e_CH36-220,e_CH38-220,e_CH39-220,e_CH40-220,e_w1086214433-220,e_w1092884227-220,e_w240959264-220,e_w364949845-220,e_w364949845-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0003,elc_spv-CHE_0003</t>
-  </si>
-  <si>
-    <t>e_CH48-225,e_CH49-225,e_CH53-225,e_CH60-225,e_w234983117-220,e_w234983117-380,e_w238138373-380,e_w260211728-225,e_w260211728-380,e_w55698557-220,e_w55698557-225,e_w802058337-220,e_w802058337-225,e_w936521586-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0017,elc_spv-CHE_0017</t>
-  </si>
-  <si>
-    <t>e_CH12-220,e_CH12-380,e_CH13-220,e_CH16-380,e_CH18-220,e_CH18-380,e_w192677427-220,e_w192677427-380,e_w52738225-220,e_w52738225-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0019,elc_spv-CHE_0019</t>
-  </si>
-  <si>
-    <t>e_CH45-220,e_w281804158-220,e_w281804158-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0023,elc_spv-CHE_0023</t>
-  </si>
-  <si>
-    <t>e_w207991759-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
-  </si>
-  <si>
-    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
-  </si>
-  <si>
-    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
-  </si>
-  <si>
-    <t>e_r5378910-220,e_w161853746-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0020,elc_spv-CHE_0020</t>
-  </si>
-  <si>
-    <t>e_CH21-220,e_CH22-220,e_CH22-380,e_CH29-220,e_CH29-380,e_CH41-380,e_w1208713169-220,e_w207993342-220,e_w207993342-380,e_w208780268-380,e_w212498548-220,e_w36348118-220,e_w365556107-220,e_w71500123-220,e_w71500123-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0001,elc_spv-CHE_0001</t>
-  </si>
-  <si>
-    <t>e_CH31-220,e_w132373704-220,e_w232662311-220,e_w44496892-220,e_w55695765-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0006,elc_spv-CHE_0006</t>
-  </si>
-  <si>
-    <t>e_w127004407-400</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0011,elc_spv-CHE_0011</t>
-  </si>
-  <si>
-    <t>e_CH46-220,e_CH47-220,e_w228003081-220,e_w391576135-220,e_w391577741-220,e_w969819301-220,e_w969819301-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0015,elc_spv-CHE_0015</t>
-  </si>
-  <si>
-    <t>e_CH50-220,e_CH56-220,e_CH58-220,e_CH59-220,e_w1327084723-220,e_w281800404-220,e_w281803398-220,e_w281815404-220,e_w35487135-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0025,elc_spv-CHE_0025</t>
-  </si>
-  <si>
-    <t>e_r7933294-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0010,elc_spv-CHE_0010</t>
-  </si>
-  <si>
-    <t>e_CH11-220,e_w109037817-220,e_w109037817-380,e_w127004407-380,e_w127004407-400,e_w27435934-220,e_w30350721-220,e_w397960460-380,e_w397960460-400,e_w88901626-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0022,elc_spv-CHE_0022</t>
-  </si>
-  <si>
-    <t>e_CH4-220,e_CH9-220,e_w455120191-220,e_w83861269-220,e_w92798668-220,e_w92873516-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0013,elc_spv-CHE_0013</t>
-  </si>
-  <si>
-    <t>e_CH15-220,e_w146225999-220,e_w159527493-220,e_w242269161-220,e_w281799252-220,e_w35002638-220,e_w35002638-380,e_w97941869-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
-  </si>
-  <si>
-    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
-  </si>
-  <si>
-    <t>e_CH17-380,e_w211907009-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
-  </si>
-  <si>
-    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
-  </si>
-  <si>
-    <t>e_w232662311-220</t>
   </si>
   <si>
     <t>e_won-CHE_0000</t>
@@ -7134,7 +7134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33BD3534-D231-4CC9-A3C4-D262AFA6178C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06969B60-2561-45DB-B282-5B2F96D49941}">
   <dimension ref="B9:AR35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="2:44">
@@ -7425,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="2:44">
@@ -7502,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="2:44">
@@ -7579,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>239</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="2:44">
@@ -7656,7 +7656,7 @@
         <v>1</v>
       </c>
       <c r="AC15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="2:44">
@@ -7733,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="AC16" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="2:29">
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="AC17" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="2:29">
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="2:29">
@@ -7964,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="2:29">
@@ -8041,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="AC20" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="2:29">
@@ -8118,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="AC21" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="2:29">
@@ -8195,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="AC22" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="2:29">
@@ -8272,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="2:29">
@@ -8349,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="AC24" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="2:29">
@@ -8426,7 +8426,7 @@
         <v>1</v>
       </c>
       <c r="AC25" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="2:29">
@@ -8503,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="AC26" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="2:29">
@@ -8580,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="AC27" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="2:29">
@@ -8657,7 +8657,7 @@
         <v>1</v>
       </c>
       <c r="AC28" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="2:29">
@@ -8734,7 +8734,7 @@
         <v>1</v>
       </c>
       <c r="AC29" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="2:29">
@@ -8811,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="AC30" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="2:29">
@@ -8888,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="AC31" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="32" spans="2:29">
@@ -8965,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="AC32" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="2:29">
@@ -9042,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="AC33" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="2:29">
@@ -9119,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="AC34" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="2:29">
@@ -9196,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -9205,7 +9205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E46D59-DA1F-42AA-8E22-F3F16073750C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10901683-3574-4BCF-B2D7-2E78334409D5}">
   <dimension ref="B9:AB36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10291,7 +10291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18966998-E24E-47C1-838D-6969C60FF586}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBCDBBBA-48AD-4B73-AA95-CAAEBEEA2CD9}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12108,7 +12108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A1EF3D7-5832-48EE-A24F-C50FA5A1BFC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0B80D2-AC66-4C83-BEB9-BAF8C8CCAFB6}">
   <dimension ref="B2:M77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12989,7 +12989,7 @@
         <v>546</v>
       </c>
       <c r="C30" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D30" t="s">
         <v>547</v>
@@ -13024,7 +13024,7 @@
         <v>547</v>
       </c>
       <c r="D31" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E31">
         <v>1</v>

--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5EBD1D1-AE42-4893-9724-9B95F4055DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B4DB1ED-A02F-43CB-86E2-C2C8B09BD17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1004,313 +1004,313 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_won-CHE_0000</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_0</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0012</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_12</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0002</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_2</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0014</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_14</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0018</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_18</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0007</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_7</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0024</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_24</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0008</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_8</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0005</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_5</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0013</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_13</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0009</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_9</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0021</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_21</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0004</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_4</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0020</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_20</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0001</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_1</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0006</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_6</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0017</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_17</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0019</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_19</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0023</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_23</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0011</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_11</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0015</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_15</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0025</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_25</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0010</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_10</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0022</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_22</t>
+  </si>
+  <si>
     <t>distr_solelc_won-CHE_0003</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell CHE_3</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0011</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_11</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0015</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_15</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0025</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_25</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0013</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_13</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0010</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_10</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0022</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_22</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0024</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_24</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0008</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_8</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0005</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_5</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0000</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_0</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0012</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_12</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0014</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_14</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0018</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_18</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0020</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_20</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0001</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_1</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0006</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_6</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0009</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_9</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0021</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_21</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0004</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_4</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0017</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_17</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0019</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_19</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0023</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_23</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0002</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_2</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0007</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_7</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
+    <t>elc_won-CHE_0000,elc_spv-CHE_0000</t>
+  </si>
+  <si>
+    <t>e_CH51-220,e_CH51-225,e_CH51-400,e_CH52-220,e_CH57-220,e_CH57-225,e_w177392130-220,e_w177392130-400,e_w239937062-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0012,elc_spv-CHE_0012</t>
+  </si>
+  <si>
+    <t>e_CH19-220,e_CH20-220,e_CH25-220,e_CH27-220,e_CH34-220,e_CH34-380,e_CH35-220,e_CH36-220,e_CH38-220,e_CH39-220,e_CH40-220,e_w1086214433-220,e_w1092884227-220,e_w240959264-220,e_w364949845-220,e_w364949845-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
+  </si>
+  <si>
+    <t>e_w232662311-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0014,elc_spv-CHE_0014</t>
+  </si>
+  <si>
+    <t>e_CH1-220,e_CH2-220,e_CH5-220,e_CH7-220,e_w108257952-220,e_w1284913429-220,e_w165513396-220,e_w165513396-380,e_w190819048-220,e_w27107779-220,e_w31308888-220,e_w33271433-220,e_w356292116-220,e_w356292116-380,e_w35840165-380,e_w50319857-220,e_w50319857-380,e_w50319857-400,e_w89405664-220,e_w89977424-220,e_w98648381-220,e_w98648381-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0018,elc_spv-CHE_0018</t>
+  </si>
+  <si>
+    <t>e_CH3-220,e_CH6-220,e_r9310861-220,e_w11282314-220,e_w147714395-220,e_w147714395-380,e_w148015471-220,e_w22899676-220,e_w240575085-220,e_w26843160-220,e_w281809991-220,e_w50561341-220,e_w87281514-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0007,elc_spv-CHE_0007</t>
+  </si>
+  <si>
+    <t>e_CH44-220,e_w212722603-220,e_w212722603-380,e_w236819191-220,e_w758943072-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
+  </si>
+  <si>
+    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
+  </si>
+  <si>
+    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
+  </si>
+  <si>
+    <t>e_r5378910-220,e_w161853746-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0013,elc_spv-CHE_0013</t>
+  </si>
+  <si>
+    <t>e_CH15-220,e_w146225999-220,e_w159527493-220,e_w242269161-220,e_w281799252-220,e_w35002638-220,e_w35002638-380,e_w97941869-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
+  </si>
+  <si>
+    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
+  </si>
+  <si>
+    <t>e_CH17-380,e_w211907009-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
+  </si>
+  <si>
+    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0020,elc_spv-CHE_0020</t>
+  </si>
+  <si>
+    <t>e_CH21-220,e_CH22-220,e_CH22-380,e_CH29-220,e_CH29-380,e_CH41-380,e_w1208713169-220,e_w207993342-220,e_w207993342-380,e_w208780268-380,e_w212498548-220,e_w36348118-220,e_w365556107-220,e_w71500123-220,e_w71500123-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0001,elc_spv-CHE_0001</t>
+  </si>
+  <si>
+    <t>e_CH31-220,e_w132373704-220,e_w232662311-220,e_w44496892-220,e_w55695765-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0006,elc_spv-CHE_0006</t>
+  </si>
+  <si>
+    <t>e_w127004407-400</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0017,elc_spv-CHE_0017</t>
+  </si>
+  <si>
+    <t>e_CH12-220,e_CH12-380,e_CH13-220,e_CH16-380,e_CH18-220,e_CH18-380,e_w192677427-220,e_w192677427-380,e_w52738225-220,e_w52738225-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0019,elc_spv-CHE_0019</t>
+  </si>
+  <si>
+    <t>e_CH45-220,e_w281804158-220,e_w281804158-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0023,elc_spv-CHE_0023</t>
+  </si>
+  <si>
+    <t>e_w207991759-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0011,elc_spv-CHE_0011</t>
+  </si>
+  <si>
+    <t>e_CH46-220,e_CH47-220,e_w228003081-220,e_w391576135-220,e_w391577741-220,e_w969819301-220,e_w969819301-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0015,elc_spv-CHE_0015</t>
+  </si>
+  <si>
+    <t>e_CH50-220,e_CH56-220,e_CH58-220,e_CH59-220,e_w1327084723-220,e_w281800404-220,e_w281803398-220,e_w281815404-220,e_w35487135-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0025,elc_spv-CHE_0025</t>
+  </si>
+  <si>
+    <t>e_r7933294-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0010,elc_spv-CHE_0010</t>
+  </si>
+  <si>
+    <t>e_CH11-220,e_w109037817-220,e_w109037817-380,e_w127004407-380,e_w127004407-400,e_w27435934-220,e_w30350721-220,e_w397960460-380,e_w397960460-400,e_w88901626-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0022,elc_spv-CHE_0022</t>
+  </si>
+  <si>
+    <t>e_CH4-220,e_CH9-220,e_w455120191-220,e_w83861269-220,e_w92798668-220,e_w92873516-220</t>
+  </si>
+  <si>
     <t>elc_won-CHE_0003,elc_spv-CHE_0003</t>
   </si>
   <si>
     <t>e_CH48-225,e_CH49-225,e_CH53-225,e_CH60-225,e_w234983117-220,e_w234983117-380,e_w238138373-380,e_w260211728-225,e_w260211728-380,e_w55698557-220,e_w55698557-225,e_w802058337-220,e_w802058337-225,e_w936521586-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0011,elc_spv-CHE_0011</t>
-  </si>
-  <si>
-    <t>e_CH46-220,e_CH47-220,e_w228003081-220,e_w391576135-220,e_w391577741-220,e_w969819301-220,e_w969819301-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0015,elc_spv-CHE_0015</t>
-  </si>
-  <si>
-    <t>e_CH50-220,e_CH56-220,e_CH58-220,e_CH59-220,e_w1327084723-220,e_w281800404-220,e_w281803398-220,e_w281815404-220,e_w35487135-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0025,elc_spv-CHE_0025</t>
-  </si>
-  <si>
-    <t>e_r7933294-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0013,elc_spv-CHE_0013</t>
-  </si>
-  <si>
-    <t>e_CH15-220,e_w146225999-220,e_w159527493-220,e_w242269161-220,e_w281799252-220,e_w35002638-220,e_w35002638-380,e_w97941869-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0010,elc_spv-CHE_0010</t>
-  </si>
-  <si>
-    <t>e_CH11-220,e_w109037817-220,e_w109037817-380,e_w127004407-380,e_w127004407-400,e_w27435934-220,e_w30350721-220,e_w397960460-380,e_w397960460-400,e_w88901626-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0022,elc_spv-CHE_0022</t>
-  </si>
-  <si>
-    <t>e_CH4-220,e_CH9-220,e_w455120191-220,e_w83861269-220,e_w92798668-220,e_w92873516-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
-  </si>
-  <si>
-    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
-  </si>
-  <si>
-    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
-  </si>
-  <si>
-    <t>e_r5378910-220,e_w161853746-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0000,elc_spv-CHE_0000</t>
-  </si>
-  <si>
-    <t>e_CH51-220,e_CH51-225,e_CH51-400,e_CH52-220,e_CH57-220,e_CH57-225,e_w177392130-220,e_w177392130-400,e_w239937062-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0012,elc_spv-CHE_0012</t>
-  </si>
-  <si>
-    <t>e_CH19-220,e_CH20-220,e_CH25-220,e_CH27-220,e_CH34-220,e_CH34-380,e_CH35-220,e_CH36-220,e_CH38-220,e_CH39-220,e_CH40-220,e_w1086214433-220,e_w1092884227-220,e_w240959264-220,e_w364949845-220,e_w364949845-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0014,elc_spv-CHE_0014</t>
-  </si>
-  <si>
-    <t>e_CH1-220,e_CH2-220,e_CH5-220,e_CH7-220,e_w108257952-220,e_w1284913429-220,e_w165513396-220,e_w165513396-380,e_w190819048-220,e_w27107779-220,e_w31308888-220,e_w33271433-220,e_w356292116-220,e_w356292116-380,e_w35840165-380,e_w50319857-220,e_w50319857-380,e_w50319857-400,e_w89405664-220,e_w89977424-220,e_w98648381-220,e_w98648381-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0018,elc_spv-CHE_0018</t>
-  </si>
-  <si>
-    <t>e_CH3-220,e_CH6-220,e_r9310861-220,e_w11282314-220,e_w147714395-220,e_w147714395-380,e_w148015471-220,e_w22899676-220,e_w240575085-220,e_w26843160-220,e_w281809991-220,e_w50561341-220,e_w87281514-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0020,elc_spv-CHE_0020</t>
-  </si>
-  <si>
-    <t>e_CH21-220,e_CH22-220,e_CH22-380,e_CH29-220,e_CH29-380,e_CH41-380,e_w1208713169-220,e_w207993342-220,e_w207993342-380,e_w208780268-380,e_w212498548-220,e_w36348118-220,e_w365556107-220,e_w71500123-220,e_w71500123-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0001,elc_spv-CHE_0001</t>
-  </si>
-  <si>
-    <t>e_CH31-220,e_w132373704-220,e_w232662311-220,e_w44496892-220,e_w55695765-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0006,elc_spv-CHE_0006</t>
-  </si>
-  <si>
-    <t>e_w127004407-400</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
-  </si>
-  <si>
-    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
-  </si>
-  <si>
-    <t>e_CH17-380,e_w211907009-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
-  </si>
-  <si>
-    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0017,elc_spv-CHE_0017</t>
-  </si>
-  <si>
-    <t>e_CH12-220,e_CH12-380,e_CH13-220,e_CH16-380,e_CH18-220,e_CH18-380,e_w192677427-220,e_w192677427-380,e_w52738225-220,e_w52738225-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0019,elc_spv-CHE_0019</t>
-  </si>
-  <si>
-    <t>e_CH45-220,e_w281804158-220,e_w281804158-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0023,elc_spv-CHE_0023</t>
-  </si>
-  <si>
-    <t>e_w207991759-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
-  </si>
-  <si>
-    <t>e_w232662311-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0007,elc_spv-CHE_0007</t>
-  </si>
-  <si>
-    <t>e_CH44-220,e_w212722603-220,e_w212722603-380,e_w236819191-220,e_w758943072-220</t>
   </si>
   <si>
     <t>e_won-CHE_0000</t>
@@ -7134,7 +7134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06969B60-2561-45DB-B282-5B2F96D49941}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C333FB5-750C-4238-B48F-BDF9AA1343AF}">
   <dimension ref="B9:AR35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7306,10 +7306,10 @@
         <v>240</v>
       </c>
       <c r="M11">
-        <v>2.3692500000000001</v>
+        <v>1.4481085481682499</v>
       </c>
       <c r="N11">
-        <v>0.17487833899999999</v>
+        <v>0.1748783388823357</v>
       </c>
       <c r="P11" t="s">
         <v>290</v>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="2:44">
@@ -7383,10 +7383,10 @@
         <v>242</v>
       </c>
       <c r="M12">
-        <v>3.6675</v>
+        <v>1.9842252367079387</v>
       </c>
       <c r="N12">
-        <v>0.16684649600000001</v>
+        <v>0.16684649586809219</v>
       </c>
       <c r="P12" t="s">
         <v>290</v>
@@ -7425,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="2:44">
@@ -7460,10 +7460,10 @@
         <v>244</v>
       </c>
       <c r="M13">
-        <v>4.0867500000000003</v>
+        <v>2.0592097501587974</v>
       </c>
       <c r="N13">
-        <v>0.163709148</v>
+        <v>0.1637091484035117</v>
       </c>
       <c r="P13" t="s">
         <v>290</v>
@@ -7502,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="2:44">
@@ -7537,10 +7537,10 @@
         <v>246</v>
       </c>
       <c r="M14">
-        <v>0.27900000000000003</v>
+        <v>0.17153533917986757</v>
       </c>
       <c r="N14">
-        <v>0.191499945</v>
+        <v>0.19149994531508041</v>
       </c>
       <c r="P14" t="s">
         <v>290</v>
@@ -7579,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="2:44">
@@ -7614,10 +7614,10 @@
         <v>248</v>
       </c>
       <c r="M15">
-        <v>2.7719999999999998</v>
+        <v>1.579447229248103</v>
       </c>
       <c r="N15">
-        <v>0.17244794099999999</v>
+        <v>0.17244794072124439</v>
       </c>
       <c r="P15" t="s">
         <v>290</v>
@@ -7656,7 +7656,7 @@
         <v>1</v>
       </c>
       <c r="AC15" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="2:44">
@@ -7691,10 +7691,10 @@
         <v>250</v>
       </c>
       <c r="M16">
-        <v>3.3885000000000001</v>
+        <v>1.8220788404653914</v>
       </c>
       <c r="N16">
-        <v>0.16438530300000001</v>
+        <v>0.16438530346263561</v>
       </c>
       <c r="P16" t="s">
         <v>290</v>
@@ -7733,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="AC16" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="2:29">
@@ -7768,10 +7768,10 @@
         <v>252</v>
       </c>
       <c r="M17">
-        <v>4.6897500000000001</v>
+        <v>2.4346755223162373</v>
       </c>
       <c r="N17">
-        <v>0.155814218</v>
+        <v>0.1558142184081644</v>
       </c>
       <c r="P17" t="s">
         <v>290</v>
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="AC17" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="2:29">
@@ -7845,10 +7845,10 @@
         <v>254</v>
       </c>
       <c r="M18">
-        <v>4.725E-2</v>
+        <v>2.8756996303142331E-2</v>
       </c>
       <c r="N18">
-        <v>0.20930892200000001</v>
+        <v>0.20930892224138251</v>
       </c>
       <c r="P18" t="s">
         <v>290</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="2:29">
@@ -7922,10 +7922,10 @@
         <v>256</v>
       </c>
       <c r="M19">
-        <v>0.45524999999999999</v>
+        <v>0.26997383720930235</v>
       </c>
       <c r="N19">
-        <v>0.18992324199999999</v>
+        <v>0.18992324175161571</v>
       </c>
       <c r="P19" t="s">
         <v>290</v>
@@ -7964,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="2:29">
@@ -7999,10 +7999,10 @@
         <v>258</v>
       </c>
       <c r="M20">
-        <v>3.0750000000000002</v>
+        <v>1.8587214788851067</v>
       </c>
       <c r="N20">
-        <v>0.16490429000000001</v>
+        <v>0.1649042899045059</v>
       </c>
       <c r="P20" t="s">
         <v>290</v>
@@ -8041,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="AC20" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="2:29">
@@ -8076,10 +8076,10 @@
         <v>260</v>
       </c>
       <c r="M21">
-        <v>3.0960000000000001</v>
+        <v>1.8101872659176026</v>
       </c>
       <c r="N21">
-        <v>0.155171543</v>
+        <v>0.1551715433802105</v>
       </c>
       <c r="P21" t="s">
         <v>290</v>
@@ -8118,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="AC21" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="2:29">
@@ -8153,10 +8153,10 @@
         <v>262</v>
       </c>
       <c r="M22">
-        <v>0.13950000000000001</v>
+        <v>8.2354980303882955E-2</v>
       </c>
       <c r="N22">
-        <v>0.19528572999999999</v>
+        <v>0.19528573025258039</v>
       </c>
       <c r="P22" t="s">
         <v>290</v>
@@ -8195,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="AC22" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="2:29">
@@ -8230,10 +8230,10 @@
         <v>264</v>
       </c>
       <c r="M23">
-        <v>8.2500000000000004E-3</v>
+        <v>4.3897763578274757E-3</v>
       </c>
       <c r="N23">
-        <v>0.19633772999999999</v>
+        <v>0.19633772958479789</v>
       </c>
       <c r="P23" t="s">
         <v>290</v>
@@ -8272,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="2:29">
@@ -8307,10 +8307,10 @@
         <v>266</v>
       </c>
       <c r="M24">
-        <v>1.9815</v>
+        <v>1.2298670247245116</v>
       </c>
       <c r="N24">
-        <v>0.16962670899999999</v>
+        <v>0.16962670935478111</v>
       </c>
       <c r="P24" t="s">
         <v>290</v>
@@ -8349,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="AC24" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="2:29">
@@ -8384,10 +8384,10 @@
         <v>268</v>
       </c>
       <c r="M25">
-        <v>2.6587499999999999</v>
+        <v>1.5659439033006963</v>
       </c>
       <c r="N25">
-        <v>0.15882470100000001</v>
+        <v>0.1588247014810453</v>
       </c>
       <c r="P25" t="s">
         <v>290</v>
@@ -8426,7 +8426,7 @@
         <v>1</v>
       </c>
       <c r="AC25" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="2:29">
@@ -8461,10 +8461,10 @@
         <v>270</v>
       </c>
       <c r="M26">
-        <v>0.44700000000000001</v>
+        <v>0.41030523108176736</v>
       </c>
       <c r="N26">
-        <v>0.17657059999999999</v>
+        <v>0.17657060019791321</v>
       </c>
       <c r="P26" t="s">
         <v>290</v>
@@ -8503,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="AC26" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="2:29">
@@ -8538,10 +8538,10 @@
         <v>272</v>
       </c>
       <c r="M27">
-        <v>0.747</v>
+        <v>0.4684507225739995</v>
       </c>
       <c r="N27">
-        <v>0.17519485900000001</v>
+        <v>0.1751948590908658</v>
       </c>
       <c r="P27" t="s">
         <v>290</v>
@@ -8580,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="AC27" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="2:29">
@@ -8615,10 +8615,10 @@
         <v>274</v>
       </c>
       <c r="M28">
-        <v>3.5550000000000002</v>
+        <v>2.1530929285090701</v>
       </c>
       <c r="N28">
-        <v>0.16076159100000001</v>
+        <v>0.1607615908692181</v>
       </c>
       <c r="P28" t="s">
         <v>290</v>
@@ -8657,7 +8657,7 @@
         <v>1</v>
       </c>
       <c r="AC28" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="2:29">
@@ -8692,10 +8692,10 @@
         <v>276</v>
       </c>
       <c r="M29">
-        <v>0.32174999999999998</v>
+        <v>0.26063177662951398</v>
       </c>
       <c r="N29">
-        <v>0.17625307000000001</v>
+        <v>0.17625306989902101</v>
       </c>
       <c r="P29" t="s">
         <v>290</v>
@@ -8734,7 +8734,7 @@
         <v>1</v>
       </c>
       <c r="AC29" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="2:29">
@@ -8769,10 +8769,10 @@
         <v>278</v>
       </c>
       <c r="M30">
-        <v>1.125E-2</v>
+        <v>6.1797040380237251E-3</v>
       </c>
       <c r="N30">
-        <v>0.19011715400000001</v>
+        <v>0.19011715424716041</v>
       </c>
       <c r="P30" t="s">
         <v>290</v>
@@ -8811,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="AC30" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="2:29">
@@ -8846,10 +8846,10 @@
         <v>280</v>
       </c>
       <c r="M31">
-        <v>0.48225000000000001</v>
+        <v>0.29639120965667998</v>
       </c>
       <c r="N31">
-        <v>0.17614020399999999</v>
+        <v>0.17614020399124761</v>
       </c>
       <c r="P31" t="s">
         <v>290</v>
@@ -8888,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="AC31" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="2:29">
@@ -8923,10 +8923,10 @@
         <v>282</v>
       </c>
       <c r="M32">
-        <v>4.6665000000000001</v>
+        <v>2.8215057141926869</v>
       </c>
       <c r="N32">
-        <v>0.160248315</v>
+        <v>0.16024831540946691</v>
       </c>
       <c r="P32" t="s">
         <v>290</v>
@@ -8965,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="AC32" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="2:29">
@@ -9000,10 +9000,10 @@
         <v>284</v>
       </c>
       <c r="M33">
-        <v>1.35E-2</v>
+        <v>8.5493602671339302E-3</v>
       </c>
       <c r="N33">
-        <v>0.18124375000000001</v>
+        <v>0.18124375048287089</v>
       </c>
       <c r="P33" t="s">
         <v>290</v>
@@ -9042,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="AC33" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" spans="2:29">
@@ -9077,10 +9077,10 @@
         <v>286</v>
       </c>
       <c r="M34">
-        <v>6.7499999999999999E-3</v>
+        <v>3.7915202381444578E-3</v>
       </c>
       <c r="N34">
-        <v>0.197498858</v>
+        <v>0.19749885808161249</v>
       </c>
       <c r="P34" t="s">
         <v>290</v>
@@ -9119,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="AC34" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="2:29">
@@ -9154,10 +9154,10 @@
         <v>288</v>
       </c>
       <c r="M35">
-        <v>2.2499999999999998E-3</v>
+        <v>1.1915835896675682E-3</v>
       </c>
       <c r="N35">
-        <v>0.184571821</v>
+        <v>0.1845718208438536</v>
       </c>
       <c r="P35" t="s">
         <v>290</v>
@@ -9196,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -9205,7 +9205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10901683-3574-4BCF-B2D7-2E78334409D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E83A4B-A524-4D4A-AB47-71377172CFA7}">
   <dimension ref="B9:AB36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9329,7 +9329,7 @@
         <v>446</v>
       </c>
       <c r="M11">
-        <v>3.3975</v>
+        <v>1.9495723062423211</v>
       </c>
       <c r="N11">
         <v>3.4340724851371601E-2</v>
@@ -9367,7 +9367,7 @@
         <v>447</v>
       </c>
       <c r="M12">
-        <v>7.4332500000000001</v>
+        <v>5.4484134852470127</v>
       </c>
       <c r="N12">
         <v>9.4605520907724894E-2</v>
@@ -9405,7 +9405,7 @@
         <v>448</v>
       </c>
       <c r="M13">
-        <v>7.5884999999999998</v>
+        <v>5.5300750395968263</v>
       </c>
       <c r="N13">
         <v>0.18337776623437799</v>
@@ -9443,7 +9443,7 @@
         <v>449</v>
       </c>
       <c r="M14">
-        <v>0.55874999999999997</v>
+        <v>0.3869841025685466</v>
       </c>
       <c r="N14">
         <v>9.6433556389264995E-3</v>
@@ -9481,7 +9481,7 @@
         <v>450</v>
       </c>
       <c r="M15">
-        <v>4.6582499999999998</v>
+        <v>3.0790570281938239</v>
       </c>
       <c r="N15">
         <v>3.3416012310939797E-2</v>
@@ -9519,7 +9519,7 @@
         <v>451</v>
       </c>
       <c r="M16">
-        <v>6.7035</v>
+        <v>4.8810223774085832</v>
       </c>
       <c r="N16">
         <v>0.10904849809575221</v>
@@ -9557,7 +9557,7 @@
         <v>452</v>
       </c>
       <c r="M17">
-        <v>7.6980000000000004</v>
+        <v>5.2637138388739624</v>
       </c>
       <c r="N17">
         <v>0.15124373583078471</v>
@@ -9595,7 +9595,7 @@
         <v>453</v>
       </c>
       <c r="M18">
-        <v>0.35399999999999998</v>
+        <v>0.32478654343807761</v>
       </c>
       <c r="N18">
         <v>9.7201838396387998E-3</v>
@@ -9633,7 +9633,7 @@
         <v>454</v>
       </c>
       <c r="M19">
-        <v>1.0920000000000001</v>
+        <v>0.82158139534883734</v>
       </c>
       <c r="N19">
         <v>1.48728579334318E-2</v>
@@ -9671,7 +9671,7 @@
         <v>455</v>
       </c>
       <c r="M20">
-        <v>6.1920000000000002</v>
+        <v>4.3332785211148934</v>
       </c>
       <c r="N20">
         <v>5.6562862859018202E-2</v>
@@ -9709,7 +9709,7 @@
         <v>456</v>
       </c>
       <c r="M21">
-        <v>6.3525</v>
+        <v>4.5427400681867214</v>
       </c>
       <c r="N21">
         <v>9.1718896536609501E-2</v>
@@ -9747,7 +9747,7 @@
         <v>457</v>
       </c>
       <c r="M22">
-        <v>0.30525000000000002</v>
+        <v>0.2222135031502753</v>
       </c>
       <c r="N22">
         <v>1.22210117108462E-2</v>
@@ -9785,7 +9785,7 @@
         <v>458</v>
       </c>
       <c r="M23">
-        <v>0.46800000000000003</v>
+        <v>0.4632111530641882</v>
       </c>
       <c r="N23">
         <v>1.50049887647238E-2</v>
@@ -9823,7 +9823,7 @@
         <v>459</v>
       </c>
       <c r="M24">
-        <v>2.9737499999999999</v>
+        <v>1.7426414691899286</v>
       </c>
       <c r="N24">
         <v>2.1682676131496301E-2</v>
@@ -9861,7 +9861,7 @@
         <v>460</v>
       </c>
       <c r="M25">
-        <v>7.33575</v>
+        <v>5.7700877580207592</v>
       </c>
       <c r="N25">
         <v>8.4808315126564907E-2</v>
@@ -9899,7 +9899,7 @@
         <v>461</v>
       </c>
       <c r="M26">
-        <v>0.10725</v>
+        <v>3.6439944134078216E-2</v>
       </c>
       <c r="N26">
         <v>1.8369649268974501E-2</v>
@@ -9975,7 +9975,7 @@
         <v>464</v>
       </c>
       <c r="M28">
-        <v>1.2615000000000001</v>
+        <v>0.79360563220340441</v>
       </c>
       <c r="N28">
         <v>1.0887589015734001E-2</v>
@@ -10013,7 +10013,7 @@
         <v>465</v>
       </c>
       <c r="M29">
-        <v>6.7882499999999997</v>
+        <v>4.6353949297463997</v>
       </c>
       <c r="N29">
         <v>7.537980374929E-2</v>
@@ -10051,7 +10051,7 @@
         <v>466</v>
       </c>
       <c r="M30">
-        <v>0.183</v>
+        <v>6.0975756649342704E-2</v>
       </c>
       <c r="N30">
         <v>1.32900004537707E-2</v>
@@ -10089,7 +10089,7 @@
         <v>467</v>
       </c>
       <c r="M31">
-        <v>0.90225</v>
+        <v>0.89566379051362788</v>
       </c>
       <c r="N31">
         <v>2.11273443568681E-2</v>
@@ -10127,7 +10127,7 @@
         <v>468</v>
       </c>
       <c r="M32">
-        <v>0.89849999999999997</v>
+        <v>0.60214259338433851</v>
       </c>
       <c r="N32">
         <v>9.8108031047365006E-3</v>
@@ -10165,7 +10165,7 @@
         <v>469</v>
       </c>
       <c r="M33">
-        <v>4.8682499999999997</v>
+        <v>2.0462720932774983</v>
       </c>
       <c r="N33">
         <v>3.5737648954593297E-2</v>
@@ -10203,7 +10203,7 @@
         <v>470</v>
       </c>
       <c r="M34">
-        <v>0.27600000000000002</v>
+        <v>0.26650071081429566</v>
       </c>
       <c r="N34">
         <v>7.7924913067907E-3</v>
@@ -10241,7 +10241,7 @@
         <v>471</v>
       </c>
       <c r="M35">
-        <v>0.85575000000000001</v>
+        <v>0.85237680343725308</v>
       </c>
       <c r="N35">
         <v>1.57014025480663E-2</v>
@@ -10279,7 +10279,7 @@
         <v>472</v>
       </c>
       <c r="M36">
-        <v>0.71025000000000005</v>
+        <v>0.70866289780672964</v>
       </c>
       <c r="N36">
         <v>1.9178235263115299E-2</v>
@@ -10291,7 +10291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBCDBBBA-48AD-4B73-AA95-CAAEBEEA2CD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04DE08C1-5DB0-41E0-B7FF-1EA08B2BBAE2}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12108,7 +12108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0B80D2-AC66-4C83-BEB9-BAF8C8CCAFB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44DE2F40-C4F5-4208-A031-38AD20D479BD}">
   <dimension ref="B2:M77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12989,7 +12989,7 @@
         <v>546</v>
       </c>
       <c r="C30" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D30" t="s">
         <v>547</v>
@@ -13024,7 +13024,7 @@
         <v>547</v>
       </c>
       <c r="D31" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E31">
         <v>1</v>

--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B4DB1ED-A02F-43CB-86E2-C2C8B09BD17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{966C3210-5B79-4FC4-93AF-6024AD151B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1004,16 +1004,136 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_won-CHE_0011</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_11</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0015</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_15</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0025</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_25</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0010</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_10</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0022</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_22</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0014</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_14</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0018</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_18</t>
+  </si>
+  <si>
     <t>distr_solelc_won-CHE_0000</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell CHE_0</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_won-CHE_0003</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_3</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0002</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_2</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0007</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_7</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0009</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_9</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0021</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_21</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0004</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_4</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0020</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_20</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0001</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_1</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0006</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_6</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0024</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_24</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0008</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_8</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0005</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_5</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0013</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_13</t>
   </si>
   <si>
     <t>distr_solelc_won-CHE_0012</t>
@@ -1022,90 +1142,6 @@
     <t>connecting solar and wind to buses in grid cell CHE_12</t>
   </si>
   <si>
-    <t>distr_solelc_won-CHE_0002</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_2</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0014</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_14</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0018</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_18</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0007</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_7</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0024</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_24</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0008</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_8</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0005</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_5</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0013</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_13</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0009</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_9</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0021</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_21</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0004</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_4</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0020</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_20</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0001</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_1</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0006</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_6</t>
-  </si>
-  <si>
     <t>distr_solelc_won-CHE_0017</t>
   </si>
   <si>
@@ -1124,141 +1160,141 @@
     <t>connecting solar and wind to buses in grid cell CHE_23</t>
   </si>
   <si>
-    <t>distr_solelc_won-CHE_0011</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_11</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0015</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_15</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0025</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_25</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0010</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_10</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0022</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_22</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0003</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_3</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
+    <t>elc_won-CHE_0011,elc_spv-CHE_0011</t>
+  </si>
+  <si>
+    <t>e_CH46-220,e_CH47-220,e_w228003081-220,e_w391576135-220,e_w391577741-220,e_w969819301-220,e_w969819301-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0015,elc_spv-CHE_0015</t>
+  </si>
+  <si>
+    <t>e_CH50-220,e_CH56-220,e_CH58-220,e_CH59-220,e_w1327084723-220,e_w281800404-220,e_w281803398-220,e_w281815404-220,e_w35487135-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0025,elc_spv-CHE_0025</t>
+  </si>
+  <si>
+    <t>e_r7933294-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0010,elc_spv-CHE_0010</t>
+  </si>
+  <si>
+    <t>e_CH11-220,e_w109037817-220,e_w109037817-380,e_w127004407-380,e_w127004407-400,e_w27435934-220,e_w30350721-220,e_w397960460-380,e_w397960460-400,e_w88901626-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0022,elc_spv-CHE_0022</t>
+  </si>
+  <si>
+    <t>e_CH4-220,e_CH9-220,e_w455120191-220,e_w83861269-220,e_w92798668-220,e_w92873516-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0014,elc_spv-CHE_0014</t>
+  </si>
+  <si>
+    <t>e_CH1-220,e_CH2-220,e_CH5-220,e_CH7-220,e_w108257952-220,e_w1284913429-220,e_w165513396-220,e_w165513396-380,e_w190819048-220,e_w27107779-220,e_w31308888-220,e_w33271433-220,e_w356292116-220,e_w356292116-380,e_w35840165-380,e_w50319857-220,e_w50319857-380,e_w50319857-400,e_w89405664-220,e_w89977424-220,e_w98648381-220,e_w98648381-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0018,elc_spv-CHE_0018</t>
+  </si>
+  <si>
+    <t>e_CH3-220,e_CH6-220,e_r9310861-220,e_w11282314-220,e_w147714395-220,e_w147714395-380,e_w148015471-220,e_w22899676-220,e_w240575085-220,e_w26843160-220,e_w281809991-220,e_w50561341-220,e_w87281514-220</t>
+  </si>
+  <si>
     <t>elc_won-CHE_0000,elc_spv-CHE_0000</t>
   </si>
   <si>
     <t>e_CH51-220,e_CH51-225,e_CH51-400,e_CH52-220,e_CH57-220,e_CH57-225,e_w177392130-220,e_w177392130-400,e_w239937062-220</t>
   </si>
   <si>
+    <t>elc_won-CHE_0003,elc_spv-CHE_0003</t>
+  </si>
+  <si>
+    <t>e_CH48-225,e_CH49-225,e_CH53-225,e_CH60-225,e_w234983117-220,e_w234983117-380,e_w238138373-380,e_w260211728-225,e_w260211728-380,e_w55698557-220,e_w55698557-225,e_w802058337-220,e_w802058337-225,e_w936521586-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
+  </si>
+  <si>
+    <t>e_w232662311-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0007,elc_spv-CHE_0007</t>
+  </si>
+  <si>
+    <t>e_CH44-220,e_w212722603-220,e_w212722603-380,e_w236819191-220,e_w758943072-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
+  </si>
+  <si>
+    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
+  </si>
+  <si>
+    <t>e_CH17-380,e_w211907009-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
+  </si>
+  <si>
+    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0020,elc_spv-CHE_0020</t>
+  </si>
+  <si>
+    <t>e_CH21-220,e_CH22-220,e_CH22-380,e_CH29-220,e_CH29-380,e_CH41-380,e_w1208713169-220,e_w207993342-220,e_w207993342-380,e_w208780268-380,e_w212498548-220,e_w36348118-220,e_w365556107-220,e_w71500123-220,e_w71500123-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0001,elc_spv-CHE_0001</t>
+  </si>
+  <si>
+    <t>e_CH31-220,e_w132373704-220,e_w232662311-220,e_w44496892-220,e_w55695765-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0006,elc_spv-CHE_0006</t>
+  </si>
+  <si>
+    <t>e_w127004407-400</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
+  </si>
+  <si>
+    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
+  </si>
+  <si>
+    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
+  </si>
+  <si>
+    <t>e_r5378910-220,e_w161853746-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0013,elc_spv-CHE_0013</t>
+  </si>
+  <si>
+    <t>e_CH15-220,e_w146225999-220,e_w159527493-220,e_w242269161-220,e_w281799252-220,e_w35002638-220,e_w35002638-380,e_w97941869-220</t>
+  </si>
+  <si>
     <t>elc_won-CHE_0012,elc_spv-CHE_0012</t>
   </si>
   <si>
     <t>e_CH19-220,e_CH20-220,e_CH25-220,e_CH27-220,e_CH34-220,e_CH34-380,e_CH35-220,e_CH36-220,e_CH38-220,e_CH39-220,e_CH40-220,e_w1086214433-220,e_w1092884227-220,e_w240959264-220,e_w364949845-220,e_w364949845-380</t>
   </si>
   <si>
-    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
-  </si>
-  <si>
-    <t>e_w232662311-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0014,elc_spv-CHE_0014</t>
-  </si>
-  <si>
-    <t>e_CH1-220,e_CH2-220,e_CH5-220,e_CH7-220,e_w108257952-220,e_w1284913429-220,e_w165513396-220,e_w165513396-380,e_w190819048-220,e_w27107779-220,e_w31308888-220,e_w33271433-220,e_w356292116-220,e_w356292116-380,e_w35840165-380,e_w50319857-220,e_w50319857-380,e_w50319857-400,e_w89405664-220,e_w89977424-220,e_w98648381-220,e_w98648381-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0018,elc_spv-CHE_0018</t>
-  </si>
-  <si>
-    <t>e_CH3-220,e_CH6-220,e_r9310861-220,e_w11282314-220,e_w147714395-220,e_w147714395-380,e_w148015471-220,e_w22899676-220,e_w240575085-220,e_w26843160-220,e_w281809991-220,e_w50561341-220,e_w87281514-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0007,elc_spv-CHE_0007</t>
-  </si>
-  <si>
-    <t>e_CH44-220,e_w212722603-220,e_w212722603-380,e_w236819191-220,e_w758943072-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
-  </si>
-  <si>
-    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
-  </si>
-  <si>
-    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
-  </si>
-  <si>
-    <t>e_r5378910-220,e_w161853746-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0013,elc_spv-CHE_0013</t>
-  </si>
-  <si>
-    <t>e_CH15-220,e_w146225999-220,e_w159527493-220,e_w242269161-220,e_w281799252-220,e_w35002638-220,e_w35002638-380,e_w97941869-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
-  </si>
-  <si>
-    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
-  </si>
-  <si>
-    <t>e_CH17-380,e_w211907009-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
-  </si>
-  <si>
-    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0020,elc_spv-CHE_0020</t>
-  </si>
-  <si>
-    <t>e_CH21-220,e_CH22-220,e_CH22-380,e_CH29-220,e_CH29-380,e_CH41-380,e_w1208713169-220,e_w207993342-220,e_w207993342-380,e_w208780268-380,e_w212498548-220,e_w36348118-220,e_w365556107-220,e_w71500123-220,e_w71500123-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0001,elc_spv-CHE_0001</t>
-  </si>
-  <si>
-    <t>e_CH31-220,e_w132373704-220,e_w232662311-220,e_w44496892-220,e_w55695765-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0006,elc_spv-CHE_0006</t>
-  </si>
-  <si>
-    <t>e_w127004407-400</t>
-  </si>
-  <si>
     <t>elc_won-CHE_0017,elc_spv-CHE_0017</t>
   </si>
   <si>
@@ -1275,42 +1311,6 @@
   </si>
   <si>
     <t>e_w207991759-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0011,elc_spv-CHE_0011</t>
-  </si>
-  <si>
-    <t>e_CH46-220,e_CH47-220,e_w228003081-220,e_w391576135-220,e_w391577741-220,e_w969819301-220,e_w969819301-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0015,elc_spv-CHE_0015</t>
-  </si>
-  <si>
-    <t>e_CH50-220,e_CH56-220,e_CH58-220,e_CH59-220,e_w1327084723-220,e_w281800404-220,e_w281803398-220,e_w281815404-220,e_w35487135-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0025,elc_spv-CHE_0025</t>
-  </si>
-  <si>
-    <t>e_r7933294-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0010,elc_spv-CHE_0010</t>
-  </si>
-  <si>
-    <t>e_CH11-220,e_w109037817-220,e_w109037817-380,e_w127004407-380,e_w127004407-400,e_w27435934-220,e_w30350721-220,e_w397960460-380,e_w397960460-400,e_w88901626-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0022,elc_spv-CHE_0022</t>
-  </si>
-  <si>
-    <t>e_CH4-220,e_CH9-220,e_w455120191-220,e_w83861269-220,e_w92798668-220,e_w92873516-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0003,elc_spv-CHE_0003</t>
-  </si>
-  <si>
-    <t>e_CH48-225,e_CH49-225,e_CH53-225,e_CH60-225,e_w234983117-220,e_w234983117-380,e_w238138373-380,e_w260211728-225,e_w260211728-380,e_w55698557-220,e_w55698557-225,e_w802058337-220,e_w802058337-225,e_w936521586-380</t>
   </si>
   <si>
     <t>e_won-CHE_0000</t>
@@ -7134,7 +7134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C333FB5-750C-4238-B48F-BDF9AA1343AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98245C3B-B567-4552-9AA8-CF6DA920915B}">
   <dimension ref="B9:AR35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7309,7 +7309,7 @@
         <v>1.4481085481682499</v>
       </c>
       <c r="N11">
-        <v>0.1748783388823357</v>
+        <v>0.17487833888233581</v>
       </c>
       <c r="P11" t="s">
         <v>290</v>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="2:44">
@@ -7425,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="2:44">
@@ -7502,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="2:44">
@@ -7579,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="2:44">
@@ -7656,7 +7656,7 @@
         <v>1</v>
       </c>
       <c r="AC15" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="2:44">
@@ -7733,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="AC16" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="2:29">
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="AC17" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="2:29">
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="2:29">
@@ -7964,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="2:29">
@@ -8041,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="AC20" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="2:29">
@@ -8118,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="AC21" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="2:29">
@@ -8195,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="AC22" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="2:29">
@@ -8272,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="2:29">
@@ -8310,7 +8310,7 @@
         <v>1.2298670247245116</v>
       </c>
       <c r="N24">
-        <v>0.16962670935478111</v>
+        <v>0.16962670935478119</v>
       </c>
       <c r="P24" t="s">
         <v>290</v>
@@ -8349,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="AC24" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="2:29">
@@ -8426,7 +8426,7 @@
         <v>1</v>
       </c>
       <c r="AC25" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="2:29">
@@ -8503,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="AC26" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="2:29">
@@ -8580,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="AC27" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="2:29">
@@ -8657,7 +8657,7 @@
         <v>1</v>
       </c>
       <c r="AC28" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="2:29">
@@ -8734,7 +8734,7 @@
         <v>1</v>
       </c>
       <c r="AC29" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" spans="2:29">
@@ -8811,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="AC30" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="2:29">
@@ -8888,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="AC31" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" spans="2:29">
@@ -8965,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="AC32" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="2:29">
@@ -9003,7 +9003,7 @@
         <v>8.5493602671339302E-3</v>
       </c>
       <c r="N33">
-        <v>0.18124375048287089</v>
+        <v>0.181243750482871</v>
       </c>
       <c r="P33" t="s">
         <v>290</v>
@@ -9042,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="AC33" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" spans="2:29">
@@ -9119,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="AC34" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="2:29">
@@ -9196,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -9205,7 +9205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E83A4B-A524-4D4A-AB47-71377172CFA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F424A360-831D-4758-A0A7-19823121D2D4}">
   <dimension ref="B9:AB36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9332,7 +9332,7 @@
         <v>1.9495723062423211</v>
       </c>
       <c r="N11">
-        <v>3.4340724851371601E-2</v>
+        <v>3.43407248230971E-2</v>
       </c>
     </row>
     <row r="12" spans="2:28">
@@ -9370,7 +9370,7 @@
         <v>5.4484134852470127</v>
       </c>
       <c r="N12">
-        <v>9.4605520907724894E-2</v>
+        <v>9.4605519946606695E-2</v>
       </c>
     </row>
     <row r="13" spans="2:28">
@@ -9408,7 +9408,7 @@
         <v>5.5300750395968263</v>
       </c>
       <c r="N13">
-        <v>0.18337776623437799</v>
+        <v>0.18337776500373579</v>
       </c>
     </row>
     <row r="14" spans="2:28">
@@ -9446,7 +9446,7 @@
         <v>0.3869841025685466</v>
       </c>
       <c r="N14">
-        <v>9.6433556389264995E-3</v>
+        <v>9.6433558919906993E-3</v>
       </c>
     </row>
     <row r="15" spans="2:28">
@@ -9484,7 +9484,7 @@
         <v>3.0790570281938239</v>
       </c>
       <c r="N15">
-        <v>3.3416012310939797E-2</v>
+        <v>3.3416011988648103E-2</v>
       </c>
     </row>
     <row r="16" spans="2:28">
@@ -9522,7 +9522,7 @@
         <v>4.8810223774085832</v>
       </c>
       <c r="N16">
-        <v>0.10904849809575221</v>
+        <v>0.1090484973217004</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -9560,7 +9560,7 @@
         <v>5.2637138388739624</v>
       </c>
       <c r="N17">
-        <v>0.15124373583078471</v>
+        <v>0.15124373474020081</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -9598,7 +9598,7 @@
         <v>0.32478654343807761</v>
       </c>
       <c r="N18">
-        <v>9.7201838396387998E-3</v>
+        <v>9.7201835686929992E-3</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -9636,7 +9636,7 @@
         <v>0.82158139534883734</v>
       </c>
       <c r="N19">
-        <v>1.48728579334318E-2</v>
+        <v>1.48728580669195E-2</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -9674,7 +9674,7 @@
         <v>4.3332785211148934</v>
       </c>
       <c r="N20">
-        <v>5.6562862859018202E-2</v>
+        <v>5.6562862203992398E-2</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -9712,7 +9712,7 @@
         <v>4.5427400681867214</v>
       </c>
       <c r="N21">
-        <v>9.1718896536609501E-2</v>
+        <v>9.1718896057032401E-2</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -9750,7 +9750,7 @@
         <v>0.2222135031502753</v>
       </c>
       <c r="N22">
-        <v>1.22210117108462E-2</v>
+        <v>1.2221011290364601E-2</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -9788,7 +9788,7 @@
         <v>0.4632111530641882</v>
       </c>
       <c r="N23">
-        <v>1.50049887647238E-2</v>
+        <v>1.50049883921675E-2</v>
       </c>
     </row>
     <row r="24" spans="2:14">
@@ -9826,7 +9826,7 @@
         <v>1.7426414691899286</v>
       </c>
       <c r="N24">
-        <v>2.1682676131496301E-2</v>
+        <v>2.1682675869008301E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14">
@@ -9864,7 +9864,7 @@
         <v>5.7700877580207592</v>
       </c>
       <c r="N25">
-        <v>8.4808315126564907E-2</v>
+        <v>8.4808314560993803E-2</v>
       </c>
     </row>
     <row r="26" spans="2:14">
@@ -9902,7 +9902,7 @@
         <v>3.6439944134078216E-2</v>
       </c>
       <c r="N26">
-        <v>1.8369649268974501E-2</v>
+        <v>1.83696490148956E-2</v>
       </c>
     </row>
     <row r="27" spans="2:14">
@@ -9940,7 +9940,7 @@
         <v>0.44850000000000001</v>
       </c>
       <c r="N27">
-        <v>2.26324893305626E-2</v>
+        <v>2.2632488991967799E-2</v>
       </c>
     </row>
     <row r="28" spans="2:14">
@@ -9978,7 +9978,7 @@
         <v>0.79360563220340441</v>
       </c>
       <c r="N28">
-        <v>1.0887589015734001E-2</v>
+        <v>1.08875889114047E-2</v>
       </c>
     </row>
     <row r="29" spans="2:14">
@@ -10016,7 +10016,7 @@
         <v>4.6353949297463997</v>
       </c>
       <c r="N29">
-        <v>7.537980374929E-2</v>
+        <v>7.5379803340346496E-2</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -10054,7 +10054,7 @@
         <v>6.0975756649342704E-2</v>
       </c>
       <c r="N30">
-        <v>1.32900004537707E-2</v>
+        <v>1.32900002666706E-2</v>
       </c>
     </row>
     <row r="31" spans="2:14">
@@ -10092,7 +10092,7 @@
         <v>0.89566379051362788</v>
       </c>
       <c r="N31">
-        <v>2.11273443568681E-2</v>
+        <v>2.1127343918585201E-2</v>
       </c>
     </row>
     <row r="32" spans="2:14">
@@ -10130,7 +10130,7 @@
         <v>0.60214259338433851</v>
       </c>
       <c r="N32">
-        <v>9.8108031047365006E-3</v>
+        <v>9.8108028581488007E-3</v>
       </c>
     </row>
     <row r="33" spans="2:14">
@@ -10168,7 +10168,7 @@
         <v>2.0462720932774983</v>
       </c>
       <c r="N33">
-        <v>3.5737648954593297E-2</v>
+        <v>3.57376484501324E-2</v>
       </c>
     </row>
     <row r="34" spans="2:14">
@@ -10206,7 +10206,7 @@
         <v>0.26650071081429566</v>
       </c>
       <c r="N34">
-        <v>7.7924913067907E-3</v>
+        <v>7.7924912363986996E-3</v>
       </c>
     </row>
     <row r="35" spans="2:14">
@@ -10244,7 +10244,7 @@
         <v>0.85237680343725308</v>
       </c>
       <c r="N35">
-        <v>1.57014025480663E-2</v>
+        <v>1.5701402216407898E-2</v>
       </c>
     </row>
     <row r="36" spans="2:14">
@@ -10282,7 +10282,7 @@
         <v>0.70866289780672964</v>
       </c>
       <c r="N36">
-        <v>1.9178235263115299E-2</v>
+        <v>1.9178234376981702E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10291,7 +10291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04DE08C1-5DB0-41E0-B7FF-1EA08B2BBAE2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DC33FF-C170-4915-95F3-9C1F024A3319}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12108,7 +12108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44DE2F40-C4F5-4208-A031-38AD20D479BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D68A1C4-A2A9-46BE-9EF0-EE85542A8427}">
   <dimension ref="B2:M77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12989,7 +12989,7 @@
         <v>546</v>
       </c>
       <c r="C30" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D30" t="s">
         <v>547</v>
@@ -13024,7 +13024,7 @@
         <v>547</v>
       </c>
       <c r="D31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E31">
         <v>1</v>

--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{966C3210-5B79-4FC4-93AF-6024AD151B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA2899AC-9DDE-436C-AC50-D90AEA34456C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1004,18 +1004,66 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_won-CHE_0014</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_14</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0018</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_18</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0003</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_3</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0007</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_7</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0024</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_24</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0008</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_8</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0005</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_5</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0002</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_2</t>
+  </si>
+  <si>
     <t>distr_solelc_won-CHE_0011</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell CHE_11</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_won-CHE_0015</t>
   </si>
   <si>
@@ -1028,6 +1076,78 @@
     <t>connecting solar and wind to buses in grid cell CHE_25</t>
   </si>
   <si>
+    <t>distr_solelc_won-CHE_0013</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_13</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0017</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_17</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0019</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_19</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0023</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_23</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0012</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_12</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0020</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_20</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0001</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_1</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0006</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_6</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0000</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_0</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0009</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_9</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0021</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_21</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0004</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_4</t>
+  </si>
+  <si>
     <t>distr_solelc_won-CHE_0010</t>
   </si>
   <si>
@@ -1040,129 +1160,57 @@
     <t>connecting solar and wind to buses in grid cell CHE_22</t>
   </si>
   <si>
-    <t>distr_solelc_won-CHE_0014</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_14</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0018</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_18</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0000</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_0</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0003</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_3</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0002</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_2</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0007</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_7</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0009</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_9</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0021</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_21</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0004</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_4</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0020</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_20</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0001</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_1</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0006</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_6</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0024</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_24</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0008</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_8</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0005</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_5</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0013</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_13</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0012</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_12</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0017</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_17</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0019</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_19</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0023</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_23</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
+    <t>elc_won-CHE_0014,elc_spv-CHE_0014</t>
+  </si>
+  <si>
+    <t>e_CH1-220,e_CH2-220,e_CH5-220,e_CH7-220,e_w108257952-220,e_w1284913429-220,e_w165513396-220,e_w165513396-380,e_w190819048-220,e_w27107779-220,e_w31308888-220,e_w33271433-220,e_w356292116-220,e_w356292116-380,e_w35840165-380,e_w50319857-220,e_w50319857-380,e_w50319857-400,e_w89405664-220,e_w89977424-220,e_w98648381-220,e_w98648381-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0018,elc_spv-CHE_0018</t>
+  </si>
+  <si>
+    <t>e_CH3-220,e_CH6-220,e_r9310861-220,e_w11282314-220,e_w147714395-220,e_w147714395-380,e_w148015471-220,e_w22899676-220,e_w240575085-220,e_w26843160-220,e_w281809991-220,e_w50561341-220,e_w87281514-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0003,elc_spv-CHE_0003</t>
+  </si>
+  <si>
+    <t>e_CH48-225,e_CH49-225,e_CH53-225,e_CH60-225,e_w234983117-220,e_w234983117-380,e_w238138373-380,e_w260211728-225,e_w260211728-380,e_w55698557-220,e_w55698557-225,e_w802058337-220,e_w802058337-225,e_w936521586-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0007,elc_spv-CHE_0007</t>
+  </si>
+  <si>
+    <t>e_CH44-220,e_w212722603-220,e_w212722603-380,e_w236819191-220,e_w758943072-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
+  </si>
+  <si>
+    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
+  </si>
+  <si>
+    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
+  </si>
+  <si>
+    <t>e_r5378910-220,e_w161853746-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
+  </si>
+  <si>
+    <t>e_w232662311-220</t>
+  </si>
+  <si>
     <t>elc_won-CHE_0011,elc_spv-CHE_0011</t>
   </si>
   <si>
@@ -1181,6 +1229,78 @@
     <t>e_r7933294-380</t>
   </si>
   <si>
+    <t>elc_won-CHE_0013,elc_spv-CHE_0013</t>
+  </si>
+  <si>
+    <t>e_CH15-220,e_w146225999-220,e_w159527493-220,e_w242269161-220,e_w281799252-220,e_w35002638-220,e_w35002638-380,e_w97941869-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0017,elc_spv-CHE_0017</t>
+  </si>
+  <si>
+    <t>e_CH12-220,e_CH12-380,e_CH13-220,e_CH16-380,e_CH18-220,e_CH18-380,e_w192677427-220,e_w192677427-380,e_w52738225-220,e_w52738225-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0019,elc_spv-CHE_0019</t>
+  </si>
+  <si>
+    <t>e_CH45-220,e_w281804158-220,e_w281804158-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0023,elc_spv-CHE_0023</t>
+  </si>
+  <si>
+    <t>e_w207991759-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0012,elc_spv-CHE_0012</t>
+  </si>
+  <si>
+    <t>e_CH19-220,e_CH20-220,e_CH25-220,e_CH27-220,e_CH34-220,e_CH34-380,e_CH35-220,e_CH36-220,e_CH38-220,e_CH39-220,e_CH40-220,e_w1086214433-220,e_w1092884227-220,e_w240959264-220,e_w364949845-220,e_w364949845-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0020,elc_spv-CHE_0020</t>
+  </si>
+  <si>
+    <t>e_CH21-220,e_CH22-220,e_CH22-380,e_CH29-220,e_CH29-380,e_CH41-380,e_w1208713169-220,e_w207993342-220,e_w207993342-380,e_w208780268-380,e_w212498548-220,e_w36348118-220,e_w365556107-220,e_w71500123-220,e_w71500123-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0001,elc_spv-CHE_0001</t>
+  </si>
+  <si>
+    <t>e_CH31-220,e_w132373704-220,e_w232662311-220,e_w44496892-220,e_w55695765-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0006,elc_spv-CHE_0006</t>
+  </si>
+  <si>
+    <t>e_w127004407-400</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0000,elc_spv-CHE_0000</t>
+  </si>
+  <si>
+    <t>e_CH51-220,e_CH51-225,e_CH51-400,e_CH52-220,e_CH57-220,e_CH57-225,e_w177392130-220,e_w177392130-400,e_w239937062-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
+  </si>
+  <si>
+    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
+  </si>
+  <si>
+    <t>e_CH17-380,e_w211907009-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
+  </si>
+  <si>
+    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
+  </si>
+  <si>
     <t>elc_won-CHE_0010,elc_spv-CHE_0010</t>
   </si>
   <si>
@@ -1191,126 +1311,6 @@
   </si>
   <si>
     <t>e_CH4-220,e_CH9-220,e_w455120191-220,e_w83861269-220,e_w92798668-220,e_w92873516-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0014,elc_spv-CHE_0014</t>
-  </si>
-  <si>
-    <t>e_CH1-220,e_CH2-220,e_CH5-220,e_CH7-220,e_w108257952-220,e_w1284913429-220,e_w165513396-220,e_w165513396-380,e_w190819048-220,e_w27107779-220,e_w31308888-220,e_w33271433-220,e_w356292116-220,e_w356292116-380,e_w35840165-380,e_w50319857-220,e_w50319857-380,e_w50319857-400,e_w89405664-220,e_w89977424-220,e_w98648381-220,e_w98648381-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0018,elc_spv-CHE_0018</t>
-  </si>
-  <si>
-    <t>e_CH3-220,e_CH6-220,e_r9310861-220,e_w11282314-220,e_w147714395-220,e_w147714395-380,e_w148015471-220,e_w22899676-220,e_w240575085-220,e_w26843160-220,e_w281809991-220,e_w50561341-220,e_w87281514-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0000,elc_spv-CHE_0000</t>
-  </si>
-  <si>
-    <t>e_CH51-220,e_CH51-225,e_CH51-400,e_CH52-220,e_CH57-220,e_CH57-225,e_w177392130-220,e_w177392130-400,e_w239937062-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0003,elc_spv-CHE_0003</t>
-  </si>
-  <si>
-    <t>e_CH48-225,e_CH49-225,e_CH53-225,e_CH60-225,e_w234983117-220,e_w234983117-380,e_w238138373-380,e_w260211728-225,e_w260211728-380,e_w55698557-220,e_w55698557-225,e_w802058337-220,e_w802058337-225,e_w936521586-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
-  </si>
-  <si>
-    <t>e_w232662311-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0007,elc_spv-CHE_0007</t>
-  </si>
-  <si>
-    <t>e_CH44-220,e_w212722603-220,e_w212722603-380,e_w236819191-220,e_w758943072-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
-  </si>
-  <si>
-    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
-  </si>
-  <si>
-    <t>e_CH17-380,e_w211907009-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
-  </si>
-  <si>
-    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0020,elc_spv-CHE_0020</t>
-  </si>
-  <si>
-    <t>e_CH21-220,e_CH22-220,e_CH22-380,e_CH29-220,e_CH29-380,e_CH41-380,e_w1208713169-220,e_w207993342-220,e_w207993342-380,e_w208780268-380,e_w212498548-220,e_w36348118-220,e_w365556107-220,e_w71500123-220,e_w71500123-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0001,elc_spv-CHE_0001</t>
-  </si>
-  <si>
-    <t>e_CH31-220,e_w132373704-220,e_w232662311-220,e_w44496892-220,e_w55695765-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0006,elc_spv-CHE_0006</t>
-  </si>
-  <si>
-    <t>e_w127004407-400</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
-  </si>
-  <si>
-    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
-  </si>
-  <si>
-    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
-  </si>
-  <si>
-    <t>e_r5378910-220,e_w161853746-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0013,elc_spv-CHE_0013</t>
-  </si>
-  <si>
-    <t>e_CH15-220,e_w146225999-220,e_w159527493-220,e_w242269161-220,e_w281799252-220,e_w35002638-220,e_w35002638-380,e_w97941869-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0012,elc_spv-CHE_0012</t>
-  </si>
-  <si>
-    <t>e_CH19-220,e_CH20-220,e_CH25-220,e_CH27-220,e_CH34-220,e_CH34-380,e_CH35-220,e_CH36-220,e_CH38-220,e_CH39-220,e_CH40-220,e_w1086214433-220,e_w1092884227-220,e_w240959264-220,e_w364949845-220,e_w364949845-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0017,elc_spv-CHE_0017</t>
-  </si>
-  <si>
-    <t>e_CH12-220,e_CH12-380,e_CH13-220,e_CH16-380,e_CH18-220,e_CH18-380,e_w192677427-220,e_w192677427-380,e_w52738225-220,e_w52738225-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0019,elc_spv-CHE_0019</t>
-  </si>
-  <si>
-    <t>e_CH45-220,e_w281804158-220,e_w281804158-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0023,elc_spv-CHE_0023</t>
-  </si>
-  <si>
-    <t>e_w207991759-380</t>
   </si>
   <si>
     <t>e_won-CHE_0000</t>
@@ -7134,7 +7134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98245C3B-B567-4552-9AA8-CF6DA920915B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A609179-945C-4186-99CA-9E37A4F4D736}">
   <dimension ref="B9:AR35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="2:44">
@@ -7425,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="2:44">
@@ -7502,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="2:44">
@@ -7579,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="2:44">
@@ -7656,7 +7656,7 @@
         <v>1</v>
       </c>
       <c r="AC15" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="2:44">
@@ -7733,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="AC16" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="2:29">
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="AC17" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="2:29">
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="2:29">
@@ -7964,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="2:29">
@@ -8041,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="AC20" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="2:29">
@@ -8118,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="AC21" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="2:29">
@@ -8195,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="AC22" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="2:29">
@@ -8272,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="2:29">
@@ -8349,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="AC24" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="2:29">
@@ -8426,7 +8426,7 @@
         <v>1</v>
       </c>
       <c r="AC25" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="2:29">
@@ -8503,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="AC26" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="2:29">
@@ -8580,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="AC27" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="2:29">
@@ -8657,7 +8657,7 @@
         <v>1</v>
       </c>
       <c r="AC28" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="2:29">
@@ -8734,7 +8734,7 @@
         <v>1</v>
       </c>
       <c r="AC29" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="2:29">
@@ -8811,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="AC30" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="2:29">
@@ -8888,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="AC31" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="2:29">
@@ -8965,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="AC32" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" spans="2:29">
@@ -9042,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="AC33" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="2:29">
@@ -9119,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="AC34" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" spans="2:29">
@@ -9196,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -9205,7 +9205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F424A360-831D-4758-A0A7-19823121D2D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DC4A3D8-4056-4856-AC88-A5CD2B20564B}">
   <dimension ref="B9:AB36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10291,7 +10291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DC33FF-C170-4915-95F3-9C1F024A3319}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C9F74F-94CF-4251-A4C4-F0884A701469}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12108,7 +12108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D68A1C4-A2A9-46BE-9EF0-EE85542A8427}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6FB6CF-CD2C-459E-BBF1-DE6DB8909F0F}">
   <dimension ref="B2:M77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12989,7 +12989,7 @@
         <v>546</v>
       </c>
       <c r="C30" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D30" t="s">
         <v>547</v>
@@ -13024,7 +13024,7 @@
         <v>547</v>
       </c>
       <c r="D31" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E31">
         <v>1</v>

--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA2899AC-9DDE-436C-AC50-D90AEA34456C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97F94E87-9971-40E2-9D81-393AF591D06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1004,28 +1004,112 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_won-CHE_0011</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_11</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0015</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_15</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0025</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_25</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0003</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_3</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0010</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_10</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0022</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_22</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0012</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_12</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0017</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_17</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0019</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_19</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0023</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_23</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0000</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_0</t>
+  </si>
+  <si>
     <t>distr_solelc_won-CHE_0014</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell CHE_14</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_won-CHE_0018</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell CHE_18</t>
   </si>
   <si>
-    <t>distr_solelc_won-CHE_0003</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_3</t>
+    <t>distr_solelc_won-CHE_0002</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_2</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0024</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_24</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0008</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_8</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0005</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_5</t>
   </si>
   <si>
     <t>distr_solelc_won-CHE_0007</t>
@@ -1034,76 +1118,28 @@
     <t>connecting solar and wind to buses in grid cell CHE_7</t>
   </si>
   <si>
-    <t>distr_solelc_won-CHE_0024</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_24</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0008</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_8</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0005</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_5</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0002</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_2</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0011</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_11</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0015</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_15</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0025</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_25</t>
-  </si>
-  <si>
     <t>distr_solelc_won-CHE_0013</t>
   </si>
   <si>
     <t>connecting solar and wind to buses in grid cell CHE_13</t>
   </si>
   <si>
-    <t>distr_solelc_won-CHE_0017</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_17</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0019</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_19</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0023</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_23</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0012</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_12</t>
+    <t>distr_solelc_won-CHE_0009</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_9</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0021</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_21</t>
+  </si>
+  <si>
+    <t>distr_solelc_won-CHE_0004</t>
+  </si>
+  <si>
+    <t>connecting solar and wind to buses in grid cell CHE_4</t>
   </si>
   <si>
     <t>distr_solelc_won-CHE_0020</t>
@@ -1124,45 +1160,75 @@
     <t>connecting solar and wind to buses in grid cell CHE_6</t>
   </si>
   <si>
-    <t>distr_solelc_won-CHE_0000</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_0</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0009</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_9</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0021</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_21</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0004</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_4</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0010</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_10</t>
-  </si>
-  <si>
-    <t>distr_solelc_won-CHE_0022</t>
-  </si>
-  <si>
-    <t>connecting solar and wind to buses in grid cell CHE_22</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
+    <t>elc_won-CHE_0011,elc_spv-CHE_0011</t>
+  </si>
+  <si>
+    <t>e_CH46-220,e_CH47-220,e_w228003081-220,e_w391576135-220,e_w391577741-220,e_w969819301-220,e_w969819301-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0015,elc_spv-CHE_0015</t>
+  </si>
+  <si>
+    <t>e_CH50-220,e_CH56-220,e_CH58-220,e_CH59-220,e_w1327084723-220,e_w281800404-220,e_w281803398-220,e_w281815404-220,e_w35487135-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0025,elc_spv-CHE_0025</t>
+  </si>
+  <si>
+    <t>e_r7933294-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0003,elc_spv-CHE_0003</t>
+  </si>
+  <si>
+    <t>e_CH48-225,e_CH49-225,e_CH53-225,e_CH60-225,e_w234983117-220,e_w234983117-380,e_w238138373-380,e_w260211728-225,e_w260211728-380,e_w55698557-220,e_w55698557-225,e_w802058337-220,e_w802058337-225,e_w936521586-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0010,elc_spv-CHE_0010</t>
+  </si>
+  <si>
+    <t>e_CH11-220,e_w109037817-220,e_w109037817-380,e_w127004407-380,e_w127004407-400,e_w27435934-220,e_w30350721-220,e_w397960460-380,e_w397960460-400,e_w88901626-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0022,elc_spv-CHE_0022</t>
+  </si>
+  <si>
+    <t>e_CH4-220,e_CH9-220,e_w455120191-220,e_w83861269-220,e_w92798668-220,e_w92873516-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0012,elc_spv-CHE_0012</t>
+  </si>
+  <si>
+    <t>e_CH19-220,e_CH20-220,e_CH25-220,e_CH27-220,e_CH34-220,e_CH34-380,e_CH35-220,e_CH36-220,e_CH38-220,e_CH39-220,e_CH40-220,e_w1086214433-220,e_w1092884227-220,e_w240959264-220,e_w364949845-220,e_w364949845-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0017,elc_spv-CHE_0017</t>
+  </si>
+  <si>
+    <t>e_CH12-220,e_CH12-380,e_CH13-220,e_CH16-380,e_CH18-220,e_CH18-380,e_w192677427-220,e_w192677427-380,e_w52738225-220,e_w52738225-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0019,elc_spv-CHE_0019</t>
+  </si>
+  <si>
+    <t>e_CH45-220,e_w281804158-220,e_w281804158-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0023,elc_spv-CHE_0023</t>
+  </si>
+  <si>
+    <t>e_w207991759-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0000,elc_spv-CHE_0000</t>
+  </si>
+  <si>
+    <t>e_CH51-220,e_CH51-225,e_CH51-400,e_CH52-220,e_CH57-220,e_CH57-225,e_w177392130-220,e_w177392130-400,e_w239937062-220</t>
+  </si>
+  <si>
     <t>elc_won-CHE_0014,elc_spv-CHE_0014</t>
   </si>
   <si>
@@ -1175,10 +1241,28 @@
     <t>e_CH3-220,e_CH6-220,e_r9310861-220,e_w11282314-220,e_w147714395-220,e_w147714395-380,e_w148015471-220,e_w22899676-220,e_w240575085-220,e_w26843160-220,e_w281809991-220,e_w50561341-220,e_w87281514-220</t>
   </si>
   <si>
-    <t>elc_won-CHE_0003,elc_spv-CHE_0003</t>
-  </si>
-  <si>
-    <t>e_CH48-225,e_CH49-225,e_CH53-225,e_CH60-225,e_w234983117-220,e_w234983117-380,e_w238138373-380,e_w260211728-225,e_w260211728-380,e_w55698557-220,e_w55698557-225,e_w802058337-220,e_w802058337-225,e_w936521586-380</t>
+    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
+  </si>
+  <si>
+    <t>e_w232662311-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
+  </si>
+  <si>
+    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
+  </si>
+  <si>
+    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
+  </si>
+  <si>
+    <t>e_r5378910-220,e_w161853746-220</t>
   </si>
   <si>
     <t>elc_won-CHE_0007,elc_spv-CHE_0007</t>
@@ -1187,76 +1271,28 @@
     <t>e_CH44-220,e_w212722603-220,e_w212722603-380,e_w236819191-220,e_w758943072-220</t>
   </si>
   <si>
-    <t>elc_won-CHE_0024,elc_spv-CHE_0024</t>
-  </si>
-  <si>
-    <t>e_CH30-380,e_CH33-380,e_CH37-380,e_r7933294-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0008,elc_spv-CHE_0008</t>
-  </si>
-  <si>
-    <t>e_CH43-220,e_w209324991-220,e_w26166640-220,e_w402055336-220,e_w758315582-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0005,elc_spv-CHE_0005</t>
-  </si>
-  <si>
-    <t>e_r5378910-220,e_w161853746-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0002,elc_spv-CHE_0002</t>
-  </si>
-  <si>
-    <t>e_w232662311-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0011,elc_spv-CHE_0011</t>
-  </si>
-  <si>
-    <t>e_CH46-220,e_CH47-220,e_w228003081-220,e_w391576135-220,e_w391577741-220,e_w969819301-220,e_w969819301-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0015,elc_spv-CHE_0015</t>
-  </si>
-  <si>
-    <t>e_CH50-220,e_CH56-220,e_CH58-220,e_CH59-220,e_w1327084723-220,e_w281800404-220,e_w281803398-220,e_w281815404-220,e_w35487135-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0025,elc_spv-CHE_0025</t>
-  </si>
-  <si>
-    <t>e_r7933294-380</t>
-  </si>
-  <si>
     <t>elc_won-CHE_0013,elc_spv-CHE_0013</t>
   </si>
   <si>
     <t>e_CH15-220,e_w146225999-220,e_w159527493-220,e_w242269161-220,e_w281799252-220,e_w35002638-220,e_w35002638-380,e_w97941869-220</t>
   </si>
   <si>
-    <t>elc_won-CHE_0017,elc_spv-CHE_0017</t>
-  </si>
-  <si>
-    <t>e_CH12-220,e_CH12-380,e_CH13-220,e_CH16-380,e_CH18-220,e_CH18-380,e_w192677427-220,e_w192677427-380,e_w52738225-220,e_w52738225-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0019,elc_spv-CHE_0019</t>
-  </si>
-  <si>
-    <t>e_CH45-220,e_w281804158-220,e_w281804158-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0023,elc_spv-CHE_0023</t>
-  </si>
-  <si>
-    <t>e_w207991759-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0012,elc_spv-CHE_0012</t>
-  </si>
-  <si>
-    <t>e_CH19-220,e_CH20-220,e_CH25-220,e_CH27-220,e_CH34-220,e_CH34-380,e_CH35-220,e_CH36-220,e_CH38-220,e_CH39-220,e_CH40-220,e_w1086214433-220,e_w1092884227-220,e_w240959264-220,e_w364949845-220,e_w364949845-380</t>
+    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
+  </si>
+  <si>
+    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
+  </si>
+  <si>
+    <t>e_CH17-380,e_w211907009-220</t>
+  </si>
+  <si>
+    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
+  </si>
+  <si>
+    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
   </si>
   <si>
     <t>elc_won-CHE_0020,elc_spv-CHE_0020</t>
@@ -1275,42 +1311,6 @@
   </si>
   <si>
     <t>e_w127004407-400</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0000,elc_spv-CHE_0000</t>
-  </si>
-  <si>
-    <t>e_CH51-220,e_CH51-225,e_CH51-400,e_CH52-220,e_CH57-220,e_CH57-225,e_w177392130-220,e_w177392130-400,e_w239937062-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0009,elc_spv-CHE_0009</t>
-  </si>
-  <si>
-    <t>e_CH14-220,e_CH14-380,e_w1105061707-220,e_w1105061707-380,e_w147557680-220,e_w165254212-220,e_w402053379-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0021,elc_spv-CHE_0021</t>
-  </si>
-  <si>
-    <t>e_CH17-380,e_w211907009-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0004,elc_spv-CHE_0004</t>
-  </si>
-  <si>
-    <t>e_w111162936-220,e_w111162936-380,e_w111162936-400,e_w122720993-220,e_w194258388-220</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0010,elc_spv-CHE_0010</t>
-  </si>
-  <si>
-    <t>e_CH11-220,e_w109037817-220,e_w109037817-380,e_w127004407-380,e_w127004407-400,e_w27435934-220,e_w30350721-220,e_w397960460-380,e_w397960460-400,e_w88901626-380</t>
-  </si>
-  <si>
-    <t>elc_won-CHE_0022,elc_spv-CHE_0022</t>
-  </si>
-  <si>
-    <t>e_CH4-220,e_CH9-220,e_w455120191-220,e_w83861269-220,e_w92798668-220,e_w92873516-220</t>
   </si>
   <si>
     <t>e_won-CHE_0000</t>
@@ -7134,7 +7134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A609179-945C-4186-99CA-9E37A4F4D736}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F949A8DE-03FF-4A57-8905-CBF44CD2286E}">
   <dimension ref="B9:AR35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="2:44">
@@ -7425,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="2:44">
@@ -7502,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="2:44">
@@ -7579,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="2:44">
@@ -7656,7 +7656,7 @@
         <v>1</v>
       </c>
       <c r="AC15" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="2:44">
@@ -7733,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="AC16" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="2:29">
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="AC17" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="2:29">
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="2:29">
@@ -7964,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="2:29">
@@ -8041,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="AC20" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="2:29">
@@ -8118,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="AC21" t="s">
-        <v>287</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="2:29">
@@ -8195,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="AC22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="2:29">
@@ -8272,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="2:29">
@@ -8349,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="AC24" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="2:29">
@@ -8426,7 +8426,7 @@
         <v>1</v>
       </c>
       <c r="AC25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="2:29">
@@ -8503,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="AC26" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="2:29">
@@ -8580,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="AC27" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="2:29">
@@ -8657,7 +8657,7 @@
         <v>1</v>
       </c>
       <c r="AC28" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="2:29">
@@ -8734,7 +8734,7 @@
         <v>1</v>
       </c>
       <c r="AC29" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" spans="2:29">
@@ -8811,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="AC30" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="2:29">
@@ -8888,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="AC31" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" spans="2:29">
@@ -8965,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="AC32" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="2:29">
@@ -9042,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="AC33" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="2:29">
@@ -9119,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="AC34" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" spans="2:29">
@@ -9196,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -9205,7 +9205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DC4A3D8-4056-4856-AC88-A5CD2B20564B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B437A50-5BF0-4517-A7E3-D9B620D146EE}">
   <dimension ref="B9:AB36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10291,7 +10291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C9F74F-94CF-4251-A4C4-F0884A701469}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A98A5F-0048-4A5D-B28D-8FA745B0B16E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12108,7 +12108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6FB6CF-CD2C-459E-BBF1-DE6DB8909F0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25BB6AA1-A680-4DB1-9A94-A37A41BB4E52}">
   <dimension ref="B2:M77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12989,7 +12989,7 @@
         <v>546</v>
       </c>
       <c r="C30" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D30" t="s">
         <v>547</v>
@@ -13024,7 +13024,7 @@
         <v>547</v>
       </c>
       <c r="D31" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="E31">
         <v>1</v>
